--- a/SymWebNew/Files/Export/01. PF of-Jul-24.xlsx
+++ b/SymWebNew/Files/Export/01. PF of-Jul-24.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IFR Offline\A&amp;F\Financial Reporting\Provident Fund\Legal Docs\PF Docs\PF Software- Shampan\PF Software Review\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D3C258-2E33-4C3B-AD6B-7FC0B7DCEF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="Contribution" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="45">
   <si>
     <t>EmpCode</t>
   </si>
@@ -58,15 +52,9 @@
     <t>Salary Period</t>
   </si>
   <si>
-    <t>DGT000056</t>
-  </si>
-  <si>
     <t>Senior Executive</t>
   </si>
   <si>
-    <t>Internal Audit</t>
-  </si>
-  <si>
     <t>Dekko Isho</t>
   </si>
   <si>
@@ -158,9 +146,6 @@
   </si>
   <si>
     <t>Uthpal Saha</t>
-  </si>
-  <si>
-    <t>Md. Foysal Hossain Sohag</t>
   </si>
   <si>
     <t>Md. Anisur Rahman</t>
@@ -169,8 +154,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -504,30 +489,30 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,27 +550,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -597,33 +582,33 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -635,33 +620,33 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -673,33 +658,33 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -711,33 +696,33 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -749,33 +734,33 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -787,33 +772,33 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -825,33 +810,33 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -863,33 +848,33 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -901,86 +886,48 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>16</v>
       </c>
-      <c r="L10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1598</v>
+        <v>2205</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>2205</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
